--- a/registration_forms/045_pie_giveaway_registration--registration_forms.xlsx
+++ b/registration_forms/045_pie_giveaway_registration--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true,_'value':_'true'}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True, 'value': 'true'}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false,_'value':_'false'}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False, 'value': 'false'}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'home_delivery',_'value':_'home'}</t>
+          <t>home_delivery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Home Delivery', 'value': 'home'}</t>
+          <t>Home Delivery</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'pickup',_'value':_'pickup'}</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Pickup', 'value': 'pickup'}</t>
+          <t>Pickup</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'apple_pie',_'value':_'apple_pie'}</t>
+          <t>apple_pie</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Apple Pie', 'value': 'apple pie'}</t>
+          <t>Apple Pie</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blueberry_pie',_'value':_'blueberry_pie'}</t>
+          <t>blueberry_pie</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Blueberry Pie', 'value': 'blueberry pie'}</t>
+          <t>Blueberry Pie</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'lemon_meringue_pie',_'value':_'lemon_meringue_pie'}</t>
+          <t>lemon_meringue_pie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Lemon Meringue Pie', 'value': 'lemon meringue pie'}</t>
+          <t>Lemon Meringue Pie</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'delivery_via_email',_'value':_'delivery_via_email'}</t>
+          <t>delivery_via_email</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Delivery via email', 'value': 'delivery via email'}</t>
+          <t>Delivery via email</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'delivery_via_sms',_'value':_'delivery_via_sms'}</t>
+          <t>delivery_via_sms</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Delivery via SMS', 'value': 'delivery via SMS'}</t>
+          <t>Delivery via SMS</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'next_week',_'value':_'next_week'}</t>
+          <t>next_week</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Next week', 'value': 'next week'}</t>
+          <t>Next week</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'next_month',_'value':_'next_month'}</t>
+          <t>next_month</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Next month', 'value': 'next month'}</t>
+          <t>Next month</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'color',_'value':_'color'}</t>
+          <t>color</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Color', 'value': 'color'}</t>
+          <t>Color</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'black_and_white',_'value':_'black_and_white'}</t>
+          <t>black_and_white</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Black and White', 'value': 'black and white'}</t>
+          <t>Black and White</t>
         </is>
       </c>
     </row>
